--- a/testAutomation_v1.0/test/Manual/Builder/UmbrellaImage/UmbrellaImage_builder_image_selection_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/Builder/UmbrellaImage/UmbrellaImage_builder_image_selection_test_cases.xlsx
@@ -965,7 +965,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Broken URL: https://example.com/this-family-cover-does-not-exist-xyz.png</t>
+          <t>Broken URL: https://example.com/this-umbrella-cover-does-not-exist-xyz.png</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
